--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
@@ -2382,11 +2382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="44015415"/>
-        <c:axId val="89563634"/>
+        <c:axId val="7039422"/>
+        <c:axId val="78685335"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="44015415"/>
+        <c:axId val="7039422"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2420,7 +2420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89563634"/>
+        <c:crossAx val="78685335"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2432,7 +2432,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="89563634"/>
+        <c:axId val="78685335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2475,7 +2475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44015415"/>
+        <c:crossAx val="7039422"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3308,11 +3308,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="17978744"/>
-        <c:axId val="2212500"/>
+        <c:axId val="57654928"/>
+        <c:axId val="93963044"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="17978744"/>
+        <c:axId val="57654928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,14 +3344,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2212500"/>
+        <c:crossAx val="93963044"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="2212500"/>
+        <c:axId val="93963044"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3425,7 +3425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17978744"/>
+        <c:crossAx val="57654928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7668,7 +7668,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -8220,23 +8220,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -12268,7 +12268,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17885,15 +17885,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>86.2114148401699</v>
+        <v>87.4474203710322</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -17988,20 +17988,20 @@
       </c>
       <c r="T2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="82"/>
       <c r="X2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="H39" s="91" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="91"/>
       <c r="J39" s="91"/>
@@ -19118,7 +19118,7 @@
       <c r="P39" s="91"/>
       <c r="Q39" s="91" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
@@ -2382,11 +2382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7039422"/>
-        <c:axId val="78685335"/>
+        <c:axId val="73564123"/>
+        <c:axId val="74492333"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="7039422"/>
+        <c:axId val="73564123"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2420,7 +2420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78685335"/>
+        <c:crossAx val="74492333"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2432,7 +2432,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="78685335"/>
+        <c:axId val="74492333"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2475,7 +2475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7039422"/>
+        <c:crossAx val="73564123"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3308,11 +3308,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="57654928"/>
-        <c:axId val="93963044"/>
+        <c:axId val="43611684"/>
+        <c:axId val="56184783"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="57654928"/>
+        <c:axId val="43611684"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,14 +3344,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93963044"/>
+        <c:crossAx val="56184783"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="93963044"/>
+        <c:axId val="56184783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3425,7 +3425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57654928"/>
+        <c:crossAx val="43611684"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
@@ -2382,11 +2382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73564123"/>
-        <c:axId val="74492333"/>
+        <c:axId val="89631600"/>
+        <c:axId val="56303034"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="73564123"/>
+        <c:axId val="89631600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2420,7 +2420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74492333"/>
+        <c:crossAx val="56303034"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2432,7 +2432,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="74492333"/>
+        <c:axId val="56303034"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2475,7 +2475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73564123"/>
+        <c:crossAx val="89631600"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3308,11 +3308,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="43611684"/>
-        <c:axId val="56184783"/>
+        <c:axId val="89687342"/>
+        <c:axId val="56144750"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="43611684"/>
+        <c:axId val="89687342"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,14 +3344,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56184783"/>
+        <c:crossAx val="56144750"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="56184783"/>
+        <c:axId val="56144750"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3425,7 +3425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43611684"/>
+        <c:crossAx val="89687342"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CONTINUA.xlsx
@@ -2382,11 +2382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="89631600"/>
-        <c:axId val="56303034"/>
+        <c:axId val="95841431"/>
+        <c:axId val="41492011"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="89631600"/>
+        <c:axId val="95841431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2420,7 +2420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56303034"/>
+        <c:crossAx val="41492011"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2432,7 +2432,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="56303034"/>
+        <c:axId val="41492011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2475,7 +2475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89631600"/>
+        <c:crossAx val="95841431"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3308,11 +3308,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="89687342"/>
-        <c:axId val="56144750"/>
+        <c:axId val="21716862"/>
+        <c:axId val="40152821"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="89687342"/>
+        <c:axId val="21716862"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,14 +3344,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56144750"/>
+        <c:crossAx val="40152821"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="56144750"/>
+        <c:axId val="40152821"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3425,7 +3425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89687342"/>
+        <c:crossAx val="21716862"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
